--- a/excel-files/MUNTINLUPA/CUPANG SENIOR HIGH SCHOOL.xlsx
+++ b/excel-files/MUNTINLUPA/CUPANG SENIOR HIGH SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BFA6E7B-24A4-4725-A8AB-CF435AAFBEF5}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A04EEED7-16C9-4A4B-82B8-C5AF996FC510}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -254,7 +254,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,14 +274,6 @@
       <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -423,7 +415,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -511,35 +503,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -554,90 +522,77 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2905,8 +2860,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H57" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
-  <autoFilter ref="A1:H57" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H9" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+  <autoFilter ref="A1:H9" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
     <tableColumn id="2" xr3:uid="{56826189-DC15-4CA2-B5A0-8F4CEC09DDAB}" name="SUBJECTS"/>
@@ -2922,8 +2877,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA28" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
-  <autoFilter ref="A2:AA28" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA10" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+  <autoFilter ref="A2:AA10" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
     <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
@@ -2978,8 +2933,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA29" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
-  <autoFilter ref="A2:AA29" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA10" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+  <autoFilter ref="A2:AA10" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="25"/>
@@ -3350,7 +3305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3361,100 +3316,118 @@
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="9" customFormat="1" ht="64.900000000000006" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:8" s="7" customFormat="1" ht="64.900000000000006" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:8" ht="41.25" customHeight="1">
+    <row r="2" spans="1:8" ht="41.25" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1293</v>
+      </c>
+      <c r="D2" s="1">
+        <v>914</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2">
+        <f t="shared" ref="G2:G9" si="0">IF((C2-D2)&lt;0,0,C2-D2)</f>
+        <v>379</v>
+      </c>
+      <c r="H2" s="3">
+        <f t="shared" ref="H2:H9" si="1">IF((D2-C2)&lt;0,0,D2-C2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="21" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>9</v>
+      <c r="B3" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1293</v>
       </c>
       <c r="D3" s="1">
-        <v>914</v>
-      </c>
-      <c r="E3" s="1">
-        <v>2024</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G10" si="0">IF((C3-D3)&lt;0,0,C3-D3)</f>
-        <v>379</v>
+        <f t="shared" si="0"/>
+        <v>1293</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H10" si="1">IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="25.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>11</v>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>1293</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="4"/>
+        <v>914</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="G4" s="2">
         <f t="shared" si="0"/>
-        <v>1293</v>
+        <v>379</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+    <row r="5" spans="1:8" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>12</v>
+      <c r="B5" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C5" s="1">
         <v>1293</v>
@@ -3463,7 +3436,7 @@
         <v>914</v>
       </c>
       <c r="E5" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>10</v>
@@ -3477,12 +3450,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5">
+    <row r="6" spans="1:8" ht="38.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>13</v>
+      <c r="B6" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="C6" s="1">
         <v>1293</v>
@@ -3505,12 +3478,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="38.25">
+    <row r="7" spans="1:8" ht="39.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>14</v>
+      <c r="B7" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>1293</v>
@@ -3533,12 +3506,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+    <row r="8" spans="1:8" ht="29.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>15</v>
+      <c r="B8" s="26" t="s">
+        <v>16</v>
       </c>
       <c r="C8" s="1">
         <v>1293</v>
@@ -3561,12 +3534,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="30.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>16</v>
+      <c r="B9" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="C9" s="1">
         <v>1293</v>
@@ -3589,59 +3562,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1293</v>
-      </c>
-      <c r="D10" s="1">
-        <v>914</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="2">
-        <f t="shared" si="0"/>
-        <v>379</v>
-      </c>
-      <c r="H10" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1"/>
+    <row r="10" spans="1:8" ht="24" customHeight="1"/>
+    <row r="11" spans="1:8" ht="15"/>
     <row r="12" spans="1:8" ht="15"/>
-    <row r="13" spans="1:8" ht="15"/>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1"/>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1"/>
-    <row r="16" spans="1:8" ht="27" customHeight="1"/>
-    <row r="17" ht="23.25" customHeight="1"/>
-    <row r="18" ht="21" customHeight="1"/>
+    <row r="13" spans="1:8" ht="49.5" customHeight="1"/>
+    <row r="14" spans="1:8" ht="29.25" customHeight="1"/>
+    <row r="15" spans="1:8" ht="27" customHeight="1"/>
+    <row r="16" spans="1:8" ht="23.25" customHeight="1"/>
+    <row r="17" ht="21" customHeight="1"/>
+    <row r="18" ht="15"/>
     <row r="19" ht="15"/>
-    <row r="20" ht="15"/>
-    <row r="21" ht="28.5" customHeight="1"/>
-    <row r="22" ht="24" customHeight="1"/>
-    <row r="23" ht="15"/>
-    <row r="24" ht="27" customHeight="1"/>
+    <row r="20" ht="28.5" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="15"/>
+    <row r="23" ht="27" customHeight="1"/>
+    <row r="24" ht="33.75" customHeight="1"/>
     <row r="25" ht="33.75" customHeight="1"/>
     <row r="26" ht="33.75" customHeight="1"/>
-    <row r="27" ht="33.75" customHeight="1"/>
+    <row r="27" ht="27.75" customHeight="1"/>
     <row r="28" ht="27.75" customHeight="1"/>
     <row r="29" ht="27.75" customHeight="1"/>
     <row r="30" ht="27.75" customHeight="1"/>
     <row r="31" ht="27.75" customHeight="1"/>
     <row r="32" ht="27.75" customHeight="1"/>
     <row r="33" ht="27.75" customHeight="1"/>
-    <row r="34" ht="27.75" customHeight="1"/>
-    <row r="35" ht="39" customHeight="1"/>
+    <row r="34" ht="39" customHeight="1"/>
+    <row r="35" ht="27.75" customHeight="1"/>
     <row r="36" ht="27.75" customHeight="1"/>
     <row r="37" ht="27.75" customHeight="1"/>
     <row r="38" ht="27.75" customHeight="1"/>
@@ -3650,8 +3596,8 @@
     <row r="41" ht="27.75" customHeight="1"/>
     <row r="42" ht="27.75" customHeight="1"/>
     <row r="43" ht="27.75" customHeight="1"/>
-    <row r="44" ht="27.75" customHeight="1"/>
-    <row r="45" ht="36.75" customHeight="1"/>
+    <row r="44" ht="36.75" customHeight="1"/>
+    <row r="45" ht="27.75" customHeight="1"/>
     <row r="46" ht="27.75" customHeight="1"/>
     <row r="47" ht="27.75" customHeight="1"/>
     <row r="48" ht="27.75" customHeight="1"/>
@@ -3660,8 +3606,8 @@
     <row r="51" ht="27.75" customHeight="1"/>
     <row r="52" ht="27.75" customHeight="1"/>
     <row r="53" ht="27.75" customHeight="1"/>
-    <row r="54" ht="27.75" customHeight="1"/>
-    <row r="55" ht="39" customHeight="1"/>
+    <row r="54" ht="39" customHeight="1"/>
+    <row r="55" ht="27.75" customHeight="1"/>
     <row r="56" ht="27.75" customHeight="1"/>
     <row r="57" ht="27.75" customHeight="1"/>
     <row r="58" ht="27.75" customHeight="1"/>
@@ -3696,26 +3642,25 @@
     <row r="87" ht="27.75" customHeight="1"/>
     <row r="88" ht="27.75" customHeight="1"/>
     <row r="89" ht="27.75" customHeight="1"/>
-    <row r="90" ht="27.75" customHeight="1"/>
-    <row r="91" ht="39.75" customHeight="1"/>
+    <row r="90" ht="39.75" customHeight="1"/>
+    <row r="91" ht="27.75" customHeight="1"/>
     <row r="92" ht="27.75" customHeight="1"/>
     <row r="93" ht="27.75" customHeight="1"/>
-    <row r="94" ht="27.75" customHeight="1"/>
-    <row r="95" ht="40.5" customHeight="1"/>
-    <row r="96" ht="38.25" customHeight="1"/>
-    <row r="97" ht="42" customHeight="1"/>
-    <row r="98" ht="47.25" customHeight="1"/>
+    <row r="94" ht="40.5" customHeight="1"/>
+    <row r="95" ht="38.25" customHeight="1"/>
+    <row r="96" ht="42" customHeight="1"/>
+    <row r="97" ht="47.25" customHeight="1"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:E10" name="Textbooks"/>
-    <protectedRange sqref="F1:F10" name="SOURCE"/>
+    <protectedRange sqref="C1:E9" name="Textbooks"/>
+    <protectedRange sqref="F1:F9" name="SOURCE"/>
   </protectedRanges>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E10" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E9" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F9" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3728,7 +3673,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AA126"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -3757,158 +3702,208 @@
     <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="23" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="32" t="s">
+    <row r="1" spans="1:27" s="21" customFormat="1" ht="34.15" customHeight="1">
+      <c r="D1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33" t="s">
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="34" t="s">
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="35" t="s">
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="Q2" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="U2" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="21" t="s">
+      <c r="V2" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="21" t="s">
+      <c r="W2" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="X2" s="22" t="s">
+      <c r="X2" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="Y2" s="30" t="s">
+      <c r="Y2" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="Z2" s="30" t="s">
+      <c r="Z2" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AA2" s="19" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="38.25">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1293</v>
+      </c>
+      <c r="D3" s="4">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>10344</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4">
+        <f t="shared" ref="H3:H10" si="0">IF((D3-E3)&lt;0,0,(D3-E3))</f>
+        <v>10344</v>
+      </c>
+      <c r="I3" s="4">
+        <f t="shared" ref="I3:I10" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>10344</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
+      <c r="N3" s="4">
+        <f t="shared" ref="N3:N10" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
+        <v>10344</v>
+      </c>
+      <c r="O3" s="4">
+        <f t="shared" ref="O3:O10" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>10344</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1"/>
       <c r="S3" s="4"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
+      <c r="T3" s="4">
+        <f t="shared" ref="T3:T10" si="4">IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
+        <v>10344</v>
+      </c>
+      <c r="U3" s="4">
+        <f t="shared" ref="U3:U10" si="5">IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>10344</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1"/>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-    </row>
-    <row r="4" spans="1:27" s="5" customFormat="1" ht="38.25">
+      <c r="Z3" s="4">
+        <f t="shared" ref="Z3:Z10" si="6">IF((V3-W3)&lt;0,0,(V3-W3))</f>
+        <v>10344</v>
+      </c>
+      <c r="AA3" s="4">
+        <f t="shared" ref="AA3:AA10" si="7">IF((W3-V3)&lt;0,0,(W3-V3))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>9</v>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>1293</v>
@@ -3923,11 +3918,11 @@
       <c r="F4" s="1"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4">
-        <f t="shared" ref="H4:H28" si="0">IF((D4-E4)&lt;0,0,(D4-E4))</f>
+        <f t="shared" si="0"/>
         <v>10344</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4:I28" si="1">IF((E4-D4)&lt;0,0,(E4-D4))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J4" s="4">
@@ -3940,11 +3935,11 @@
       <c r="L4" s="1"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4">
-        <f t="shared" ref="N4:N27" si="2">IF((J4-K4)&lt;0,0,(J4-K4))</f>
+        <f t="shared" si="2"/>
         <v>10344</v>
       </c>
       <c r="O4" s="4">
-        <f t="shared" ref="O4:O27" si="3">IF((K4-J4)&lt;0,0,(K4-J4))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P4" s="4">
@@ -3957,11 +3952,11 @@
       <c r="R4" s="1"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4">
-        <f t="shared" ref="T4:T28" si="4">IF((P4-Q4)&lt;0,0,(P4-Q4))</f>
+        <f t="shared" si="4"/>
         <v>10344</v>
       </c>
       <c r="U4" s="4">
-        <f t="shared" ref="U4:U28" si="5">IF((Q4-P4)&lt;0,0,(Q4-P4))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V4" s="4">
@@ -3974,11 +3969,11 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4">
-        <f t="shared" ref="Z4:Z28" si="6">IF((V4-W4)&lt;0,0,(V4-W4))</f>
+        <f t="shared" si="6"/>
         <v>10344</v>
       </c>
       <c r="AA4" s="4">
-        <f t="shared" ref="AA4:AA28" si="7">IF((W4-V4)&lt;0,0,(W4-V4))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3986,8 +3981,8 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>11</v>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>1293</v>
@@ -4065,8 +4060,8 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
+      <c r="B6" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>1293</v>
@@ -4140,12 +4135,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="38.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>13</v>
+      <c r="B7" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="C7" s="1">
         <v>1293</v>
@@ -4223,8 +4218,8 @@
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>14</v>
+      <c r="B8" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>1293</v>
@@ -4298,12 +4293,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="38.25">
+    <row r="9" spans="1:27" ht="57.75">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>15</v>
+      <c r="B9" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="C9" s="1">
         <v>1293</v>
@@ -4377,12 +4372,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="57.75">
+    <row r="10" spans="1:27" ht="38.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>16</v>
+      <c r="B10" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="C10" s="1">
         <v>1293</v>
@@ -4456,1135 +4451,112 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="38.25">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1293</v>
-      </c>
-      <c r="D11" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>10344</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4">
-        <f t="shared" si="0"/>
-        <v>10344</v>
-      </c>
-      <c r="I11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>10344</v>
-      </c>
-      <c r="K11" s="4">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4">
-        <f t="shared" si="2"/>
-        <v>10344</v>
-      </c>
-      <c r="O11" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>10344</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4">
-        <f t="shared" si="4"/>
-        <v>10344</v>
-      </c>
-      <c r="U11" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>10344</v>
-      </c>
-      <c r="W11" s="4">
-        <v>0</v>
-      </c>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4">
-        <f t="shared" si="6"/>
-        <v>10344</v>
-      </c>
-      <c r="AA11" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="19.5">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="8"/>
-    </row>
-    <row r="13" spans="1:27" s="5" customFormat="1" ht="19.5">
-      <c r="A13" s="1"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P13" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V13" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W13" s="4"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA13" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="19.5">
-      <c r="A14" s="1"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W14" s="4"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA14" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="19.5">
-      <c r="A15" s="1"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W15" s="4"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="19.5">
-      <c r="A16" s="1"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W16" s="4"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="19.5">
-      <c r="A17" s="1"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W17" s="4"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="19.5">
-      <c r="A18" s="1"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W18" s="4"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="19.5">
-      <c r="A19" s="1"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W19" s="4"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="19.5">
-      <c r="A20" s="1"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W20" s="4"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="19.5">
-      <c r="A21" s="1"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W21" s="4"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="4"/>
-      <c r="Z21" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" s="5" customFormat="1" ht="19.5">
-      <c r="A22" s="1"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W22" s="4"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="19.5">
-      <c r="A23" s="1"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W23" s="4"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="4"/>
-      <c r="Z23" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA23" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="19.5">
-      <c r="A24" s="1"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W24" s="4"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="4"/>
-      <c r="Z24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA24" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="19.5">
-      <c r="A25" s="1"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W25" s="4"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="4"/>
-      <c r="Z25" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA25" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="19.5">
-      <c r="A26" s="1"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W26" s="4"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA26" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="19.5">
-      <c r="A27" s="1"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O27" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P27" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W27" s="4"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="4"/>
-      <c r="Z27" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA27" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="19.5">
-      <c r="A28" s="24"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="26"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="4">
-        <f t="shared" ref="N28" si="8">IF((J28-K28)&lt;0,0,(J28-K28))</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="4">
-        <f t="shared" ref="O28" si="9">IF((K28-J28)&lt;0,0,(K28-J28))</f>
-        <v>0</v>
-      </c>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V28" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W28" s="26"/>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="26"/>
-      <c r="Z28" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA28" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
+    <row r="11" spans="1:27" ht="15"/>
+    <row r="12" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
+      <c r="Z12"/>
+      <c r="AA12"/>
+    </row>
+    <row r="13" spans="1:27" ht="15"/>
+    <row r="14" spans="1:27" ht="15"/>
+    <row r="15" spans="1:27" ht="15"/>
+    <row r="16" spans="1:27" ht="15"/>
+    <row r="17" spans="1:27" ht="15"/>
+    <row r="18" spans="1:27" ht="15"/>
+    <row r="19" spans="1:27" ht="15"/>
+    <row r="20" spans="1:27" ht="15"/>
+    <row r="21" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+      <c r="W21"/>
+      <c r="X21"/>
+      <c r="Y21"/>
+      <c r="Z21"/>
+      <c r="AA21"/>
+    </row>
+    <row r="22" spans="1:27" ht="15"/>
+    <row r="23" spans="1:27" ht="15"/>
+    <row r="24" spans="1:27" ht="15"/>
+    <row r="25" spans="1:27" ht="15"/>
+    <row r="26" spans="1:27" ht="15"/>
+    <row r="27" spans="1:27" ht="15"/>
+    <row r="28" spans="1:27" ht="15"/>
     <row r="29" spans="1:27" ht="15"/>
     <row r="30" spans="1:27" ht="15"/>
-    <row r="31" spans="1:27" ht="15"/>
-    <row r="32" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32"/>
-      <c r="P32"/>
-      <c r="Q32"/>
-      <c r="R32"/>
-      <c r="S32"/>
-      <c r="T32"/>
-      <c r="U32"/>
-      <c r="V32"/>
-      <c r="W32"/>
-      <c r="X32"/>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32"/>
-    </row>
+    <row r="31" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+      <c r="S31"/>
+      <c r="T31"/>
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+      <c r="Y31"/>
+      <c r="Z31"/>
+      <c r="AA31"/>
+    </row>
+    <row r="32" spans="1:27" ht="15"/>
     <row r="33" spans="1:27" ht="15"/>
     <row r="34" spans="1:27" ht="15"/>
     <row r="35" spans="1:27" ht="15"/>
@@ -5593,36 +4565,36 @@
     <row r="38" spans="1:27" ht="15"/>
     <row r="39" spans="1:27" ht="15"/>
     <row r="40" spans="1:27" ht="15"/>
-    <row r="41" spans="1:27" ht="15"/>
-    <row r="42" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A42"/>
-      <c r="B42"/>
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="L42"/>
-      <c r="M42"/>
-      <c r="N42"/>
-      <c r="O42"/>
-      <c r="P42"/>
-      <c r="Q42"/>
-      <c r="R42"/>
-      <c r="S42"/>
-      <c r="T42"/>
-      <c r="U42"/>
-      <c r="V42"/>
-      <c r="W42"/>
-      <c r="X42"/>
-      <c r="Y42"/>
-      <c r="Z42"/>
-      <c r="AA42"/>
-    </row>
+    <row r="41" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+      <c r="S41"/>
+      <c r="T41"/>
+      <c r="U41"/>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+      <c r="Y41"/>
+      <c r="Z41"/>
+      <c r="AA41"/>
+    </row>
+    <row r="42" spans="1:27" ht="15"/>
     <row r="43" spans="1:27" ht="15"/>
     <row r="44" spans="1:27" ht="15"/>
     <row r="45" spans="1:27" ht="15"/>
@@ -5631,36 +4603,36 @@
     <row r="48" spans="1:27" ht="15"/>
     <row r="49" spans="1:27" ht="15"/>
     <row r="50" spans="1:27" ht="15"/>
-    <row r="51" spans="1:27" ht="15"/>
-    <row r="52" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A52"/>
-      <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52"/>
-      <c r="M52"/>
-      <c r="N52"/>
-      <c r="O52"/>
-      <c r="P52"/>
-      <c r="Q52"/>
-      <c r="R52"/>
-      <c r="S52"/>
-      <c r="T52"/>
-      <c r="U52"/>
-      <c r="V52"/>
-      <c r="W52"/>
-      <c r="X52"/>
-      <c r="Y52"/>
-      <c r="Z52"/>
-      <c r="AA52"/>
-    </row>
+    <row r="51" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A51"/>
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51"/>
+      <c r="O51"/>
+      <c r="P51"/>
+      <c r="Q51"/>
+      <c r="R51"/>
+      <c r="S51"/>
+      <c r="T51"/>
+      <c r="U51"/>
+      <c r="V51"/>
+      <c r="W51"/>
+      <c r="X51"/>
+      <c r="Y51"/>
+      <c r="Z51"/>
+      <c r="AA51"/>
+    </row>
+    <row r="52" spans="1:27" ht="15"/>
     <row r="53" spans="1:27" ht="15"/>
     <row r="54" spans="1:27" ht="15"/>
     <row r="55" spans="1:27" ht="15"/>
@@ -5669,36 +4641,36 @@
     <row r="58" spans="1:27" ht="15"/>
     <row r="59" spans="1:27" ht="15"/>
     <row r="60" spans="1:27" ht="15"/>
-    <row r="61" spans="1:27" ht="15"/>
-    <row r="62" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A62"/>
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
-      <c r="I62"/>
-      <c r="J62"/>
-      <c r="K62"/>
-      <c r="L62"/>
-      <c r="M62"/>
-      <c r="N62"/>
-      <c r="O62"/>
-      <c r="P62"/>
-      <c r="Q62"/>
-      <c r="R62"/>
-      <c r="S62"/>
-      <c r="T62"/>
-      <c r="U62"/>
-      <c r="V62"/>
-      <c r="W62"/>
-      <c r="X62"/>
-      <c r="Y62"/>
-      <c r="Z62"/>
-      <c r="AA62"/>
-    </row>
+    <row r="61" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
+      <c r="N61"/>
+      <c r="O61"/>
+      <c r="P61"/>
+      <c r="Q61"/>
+      <c r="R61"/>
+      <c r="S61"/>
+      <c r="T61"/>
+      <c r="U61"/>
+      <c r="V61"/>
+      <c r="W61"/>
+      <c r="X61"/>
+      <c r="Y61"/>
+      <c r="Z61"/>
+      <c r="AA61"/>
+    </row>
+    <row r="62" spans="1:27" ht="15"/>
     <row r="63" spans="1:27" ht="15"/>
     <row r="64" spans="1:27" ht="15"/>
     <row r="65" spans="1:27" ht="15"/>
@@ -5707,36 +4679,36 @@
     <row r="68" spans="1:27" ht="15"/>
     <row r="69" spans="1:27" ht="15"/>
     <row r="70" spans="1:27" ht="15"/>
-    <row r="71" spans="1:27" ht="15"/>
-    <row r="72" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A72"/>
-      <c r="B72"/>
-      <c r="C72"/>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
-      <c r="G72"/>
-      <c r="H72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-      <c r="K72"/>
-      <c r="L72"/>
-      <c r="M72"/>
-      <c r="N72"/>
-      <c r="O72"/>
-      <c r="P72"/>
-      <c r="Q72"/>
-      <c r="R72"/>
-      <c r="S72"/>
-      <c r="T72"/>
-      <c r="U72"/>
-      <c r="V72"/>
-      <c r="W72"/>
-      <c r="X72"/>
-      <c r="Y72"/>
-      <c r="Z72"/>
-      <c r="AA72"/>
-    </row>
+    <row r="71" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
+      <c r="N71"/>
+      <c r="O71"/>
+      <c r="P71"/>
+      <c r="Q71"/>
+      <c r="R71"/>
+      <c r="S71"/>
+      <c r="T71"/>
+      <c r="U71"/>
+      <c r="V71"/>
+      <c r="W71"/>
+      <c r="X71"/>
+      <c r="Y71"/>
+      <c r="Z71"/>
+      <c r="AA71"/>
+    </row>
+    <row r="72" spans="1:27" ht="15"/>
     <row r="73" spans="1:27" ht="15"/>
     <row r="74" spans="1:27" ht="15"/>
     <row r="75" spans="1:27" ht="15"/>
@@ -5745,36 +4717,36 @@
     <row r="78" spans="1:27" ht="15"/>
     <row r="79" spans="1:27" ht="15"/>
     <row r="80" spans="1:27" ht="15"/>
-    <row r="81" spans="1:27" ht="15"/>
-    <row r="82" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A82"/>
-      <c r="B82"/>
-      <c r="C82"/>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
-      <c r="G82"/>
-      <c r="H82"/>
-      <c r="I82"/>
-      <c r="J82"/>
-      <c r="K82"/>
-      <c r="L82"/>
-      <c r="M82"/>
-      <c r="N82"/>
-      <c r="O82"/>
-      <c r="P82"/>
-      <c r="Q82"/>
-      <c r="R82"/>
-      <c r="S82"/>
-      <c r="T82"/>
-      <c r="U82"/>
-      <c r="V82"/>
-      <c r="W82"/>
-      <c r="X82"/>
-      <c r="Y82"/>
-      <c r="Z82"/>
-      <c r="AA82"/>
-    </row>
+    <row r="81" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81"/>
+      <c r="I81"/>
+      <c r="J81"/>
+      <c r="K81"/>
+      <c r="L81"/>
+      <c r="M81"/>
+      <c r="N81"/>
+      <c r="O81"/>
+      <c r="P81"/>
+      <c r="Q81"/>
+      <c r="R81"/>
+      <c r="S81"/>
+      <c r="T81"/>
+      <c r="U81"/>
+      <c r="V81"/>
+      <c r="W81"/>
+      <c r="X81"/>
+      <c r="Y81"/>
+      <c r="Z81"/>
+      <c r="AA81"/>
+    </row>
+    <row r="82" spans="1:27" ht="15"/>
     <row r="83" spans="1:27" ht="15"/>
     <row r="84" spans="1:27" ht="15"/>
     <row r="85" spans="1:27" ht="15"/>
@@ -5783,36 +4755,36 @@
     <row r="88" spans="1:27" ht="15"/>
     <row r="89" spans="1:27" ht="15"/>
     <row r="90" spans="1:27" ht="15"/>
-    <row r="91" spans="1:27" ht="15"/>
-    <row r="92" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A92"/>
-      <c r="B92"/>
-      <c r="C92"/>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
-      <c r="G92"/>
-      <c r="H92"/>
-      <c r="I92"/>
-      <c r="J92"/>
-      <c r="K92"/>
-      <c r="L92"/>
-      <c r="M92"/>
-      <c r="N92"/>
-      <c r="O92"/>
-      <c r="P92"/>
-      <c r="Q92"/>
-      <c r="R92"/>
-      <c r="S92"/>
-      <c r="T92"/>
-      <c r="U92"/>
-      <c r="V92"/>
-      <c r="W92"/>
-      <c r="X92"/>
-      <c r="Y92"/>
-      <c r="Z92"/>
-      <c r="AA92"/>
-    </row>
+    <row r="91" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91"/>
+      <c r="I91"/>
+      <c r="J91"/>
+      <c r="K91"/>
+      <c r="L91"/>
+      <c r="M91"/>
+      <c r="N91"/>
+      <c r="O91"/>
+      <c r="P91"/>
+      <c r="Q91"/>
+      <c r="R91"/>
+      <c r="S91"/>
+      <c r="T91"/>
+      <c r="U91"/>
+      <c r="V91"/>
+      <c r="W91"/>
+      <c r="X91"/>
+      <c r="Y91"/>
+      <c r="Z91"/>
+      <c r="AA91"/>
+    </row>
+    <row r="92" spans="1:27" ht="15"/>
     <row r="93" spans="1:27" ht="15"/>
     <row r="94" spans="1:27" ht="15"/>
     <row r="95" spans="1:27" ht="15"/>
@@ -5821,36 +4793,36 @@
     <row r="98" spans="1:27" ht="15"/>
     <row r="99" spans="1:27" ht="15"/>
     <row r="100" spans="1:27" ht="15"/>
-    <row r="101" spans="1:27" ht="15"/>
-    <row r="102" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A102"/>
-      <c r="B102"/>
-      <c r="C102"/>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
-      <c r="I102"/>
-      <c r="J102"/>
-      <c r="K102"/>
-      <c r="L102"/>
-      <c r="M102"/>
-      <c r="N102"/>
-      <c r="O102"/>
-      <c r="P102"/>
-      <c r="Q102"/>
-      <c r="R102"/>
-      <c r="S102"/>
-      <c r="T102"/>
-      <c r="U102"/>
-      <c r="V102"/>
-      <c r="W102"/>
-      <c r="X102"/>
-      <c r="Y102"/>
-      <c r="Z102"/>
-      <c r="AA102"/>
-    </row>
+    <row r="101" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
+      <c r="L101"/>
+      <c r="M101"/>
+      <c r="N101"/>
+      <c r="O101"/>
+      <c r="P101"/>
+      <c r="Q101"/>
+      <c r="R101"/>
+      <c r="S101"/>
+      <c r="T101"/>
+      <c r="U101"/>
+      <c r="V101"/>
+      <c r="W101"/>
+      <c r="X101"/>
+      <c r="Y101"/>
+      <c r="Z101"/>
+      <c r="AA101"/>
+    </row>
+    <row r="102" spans="1:27" ht="15"/>
     <row r="103" spans="1:27" ht="15"/>
     <row r="104" spans="1:27" ht="15"/>
     <row r="105" spans="1:27" ht="15"/>
@@ -5858,36 +4830,36 @@
     <row r="107" spans="1:27" ht="15"/>
     <row r="108" spans="1:27" ht="15"/>
     <row r="109" spans="1:27" ht="15"/>
-    <row r="110" spans="1:27" ht="15"/>
-    <row r="111" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A111"/>
-      <c r="B111"/>
-      <c r="C111"/>
-      <c r="D111"/>
-      <c r="E111"/>
-      <c r="F111"/>
-      <c r="G111"/>
-      <c r="H111"/>
-      <c r="I111"/>
-      <c r="J111"/>
-      <c r="K111"/>
-      <c r="L111"/>
-      <c r="M111"/>
-      <c r="N111"/>
-      <c r="O111"/>
-      <c r="P111"/>
-      <c r="Q111"/>
-      <c r="R111"/>
-      <c r="S111"/>
-      <c r="T111"/>
-      <c r="U111"/>
-      <c r="V111"/>
-      <c r="W111"/>
-      <c r="X111"/>
-      <c r="Y111"/>
-      <c r="Z111"/>
-      <c r="AA111"/>
-    </row>
+    <row r="110" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110"/>
+      <c r="K110"/>
+      <c r="L110"/>
+      <c r="M110"/>
+      <c r="N110"/>
+      <c r="O110"/>
+      <c r="P110"/>
+      <c r="Q110"/>
+      <c r="R110"/>
+      <c r="S110"/>
+      <c r="T110"/>
+      <c r="U110"/>
+      <c r="V110"/>
+      <c r="W110"/>
+      <c r="X110"/>
+      <c r="Y110"/>
+      <c r="Z110"/>
+      <c r="AA110"/>
+    </row>
+    <row r="111" spans="1:27" ht="15"/>
     <row r="112" spans="1:27" ht="15"/>
     <row r="113" ht="15"/>
     <row r="114" ht="15"/>
@@ -5903,13 +4875,12 @@
     <row r="124" ht="15"/>
     <row r="125" ht="15"/>
     <row r="126" ht="15"/>
-    <row r="127" ht="15"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C13:C28 C2" name="Textbooks"/>
-    <protectedRange sqref="D2:F2 P2:R2 Z3:AA28 H4:I11 D13:F28 H13:I28 N28:R28 W13:X28 N3:P27 T3:V28 K13:L28 J3:J28 V2:X2 Q13:R27 J2:L2 D4:F11 K4:L11 Q4:R11 W4:X11" name="LAS"/>
-    <protectedRange sqref="S2:U2 M2:O2 Y2:AA2 G4:G11 G13:G28 M13:M28 S13:S28 Y13:Y28 Y3:Y11 M3:M11 S3:S11 G2:I2" name="SOURCE"/>
-    <protectedRange sqref="C4:C11" name="Textbooks_1"/>
+    <protectedRange sqref="C2" name="Textbooks"/>
+    <protectedRange sqref="D2:F2 P2:R2 V2:X2 H3:I10 W3:X10 J2:L2 D3:F10 N3:P10 T3:V10 K3:L10 J3:J10 Q3:R10 Z3:AA10" name="LAS"/>
+    <protectedRange sqref="S2:U2 M2:O2 Y2:AA2 G3:G10 Y3:Y10 M3:M10 S3:S10 G2:I2" name="SOURCE"/>
+    <protectedRange sqref="C3:C10" name="Textbooks_1"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -5918,14 +4889,11 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S13:S28 M13:M28 Y13:Y28 G13:G28" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
-      <formula1>"CO,RO,SDO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X13:X28 F4:F11 F13:F28 L4:L11 L13:L28 R4:R11 R13:R28 X4:X11" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 L3:L10 R3:R10 X3:X10" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G11 S3:S11 Y3:Y11 M3:M11" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G10 M3:M10 Y3:Y10 S3:S10" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5938,7 +4906,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB169"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5966,159 +4934,207 @@
     <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="23" customFormat="1" ht="34.15" customHeight="1">
-      <c r="B1" s="27"/>
-      <c r="D1" s="32" t="s">
+    <row r="1" spans="1:27" s="21" customFormat="1" ht="34.15" customHeight="1">
+      <c r="B1" s="22"/>
+      <c r="D1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33" t="s">
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="34" t="s">
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="35" t="s">
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="28" t="s">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="Q2" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="U2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="V2" s="21" t="s">
+      <c r="V2" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="W2" s="21" t="s">
+      <c r="W2" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="X2" s="22" t="s">
+      <c r="X2" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" s="30" t="s">
+      <c r="Y2" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="Z2" s="30" t="s">
+      <c r="Z2" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AA2" s="19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-    </row>
-    <row r="4" spans="1:27" ht="38.25">
+    <row r="3" spans="1:27" ht="38.25">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1293</v>
+      </c>
+      <c r="D3" s="4">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>10344</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4">
+        <f t="shared" ref="H3:H10" si="0">IF((D3-E3)&lt;0,0,(D3-E3))</f>
+        <v>10344</v>
+      </c>
+      <c r="I3" s="4">
+        <f t="shared" ref="I3:I10" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>10344</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4">
+        <f t="shared" ref="N3:N10" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
+        <v>10344</v>
+      </c>
+      <c r="O3" s="4">
+        <f t="shared" ref="O3:O10" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>10344</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4">
+        <f t="shared" ref="T3:T10" si="4">IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
+        <v>10344</v>
+      </c>
+      <c r="U3" s="4">
+        <f t="shared" ref="U3:U10" si="5">IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>10344</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4">
+        <f t="shared" ref="Z3:Z10" si="6">IF((V3-W3)&lt;0,0,(V3-W3))</f>
+        <v>10344</v>
+      </c>
+      <c r="AA3" s="4">
+        <f t="shared" ref="AA3:AA10" si="7">IF((W3-V3)&lt;0,0,(W3-V3))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>9</v>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>1293</v>
@@ -6133,11 +5149,11 @@
       <c r="F4" s="1"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4">
-        <f t="shared" ref="H4:H11" si="0">IF((D4-E4)&lt;0,0,(D4-E4))</f>
+        <f t="shared" si="0"/>
         <v>10344</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4:I11" si="1">IF((E4-D4)&lt;0,0,(E4-D4))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J4" s="4">
@@ -6148,11 +5164,11 @@
       <c r="L4" s="1"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4">
-        <f t="shared" ref="N4:N11" si="2">IF((J4-K4)&lt;0,0,(J4-K4))</f>
+        <f t="shared" si="2"/>
         <v>10344</v>
       </c>
       <c r="O4" s="4">
-        <f t="shared" ref="O4:O11" si="3">IF((K4-J4)&lt;0,0,(K4-J4))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P4" s="4">
@@ -6165,11 +5181,11 @@
       <c r="R4" s="1"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4">
-        <f t="shared" ref="T4:T11" si="4">IF((P4-Q4)&lt;0,0,(P4-Q4))</f>
+        <f t="shared" si="4"/>
         <v>10344</v>
       </c>
       <c r="U4" s="4">
-        <f t="shared" ref="U4:U11" si="5">IF((Q4-P4)&lt;0,0,(Q4-P4))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V4" s="4">
@@ -6182,11 +5198,11 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4">
-        <f t="shared" ref="Z4:Z11" si="6">IF((V4-W4)&lt;0,0,(V4-W4))</f>
+        <f t="shared" si="6"/>
         <v>10344</v>
       </c>
       <c r="AA4" s="4">
-        <f t="shared" ref="AA4:AA11" si="7">IF((W4-V4)&lt;0,0,(W4-V4))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -6194,8 +5210,8 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>11</v>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>1293</v>
@@ -6271,8 +5287,8 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
+      <c r="B6" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>1293</v>
@@ -6344,12 +5360,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="38.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>13</v>
+      <c r="B7" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="C7" s="1">
         <v>1293</v>
@@ -6425,8 +5441,8 @@
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>14</v>
+      <c r="B8" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>1293</v>
@@ -6498,12 +5514,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="38.25">
+    <row r="9" spans="1:27" ht="57.75">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>15</v>
+      <c r="B9" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="C9" s="1">
         <v>1293</v>
@@ -6575,12 +5591,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="57.75">
+    <row r="10" spans="1:27" s="5" customFormat="1" ht="38.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>16</v>
+      <c r="B10" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="C10" s="1">
         <v>1293</v>
@@ -6652,606 +5668,82 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="5" customFormat="1" ht="38.25">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1293</v>
-      </c>
-      <c r="D11" s="4">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>10344</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4">
-        <f t="shared" si="0"/>
-        <v>10344</v>
-      </c>
-      <c r="I11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="4">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>10344</v>
-      </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4">
-        <f t="shared" si="2"/>
-        <v>10344</v>
-      </c>
-      <c r="O11" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="4">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>10344</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4">
-        <f t="shared" si="4"/>
-        <v>10344</v>
-      </c>
-      <c r="U11" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="4">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>10344</v>
-      </c>
-      <c r="W11" s="4">
-        <v>0</v>
-      </c>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4">
-        <f t="shared" si="6"/>
-        <v>10344</v>
-      </c>
-      <c r="AA11" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="15">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
-    </row>
-    <row r="13" spans="1:27" ht="15">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
-      <c r="Z13" s="5"/>
-      <c r="AA13" s="5"/>
-    </row>
-    <row r="14" spans="1:27" ht="15">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
-      <c r="Z14" s="5"/>
-      <c r="AA14" s="5"/>
-    </row>
-    <row r="15" spans="1:27" ht="15">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5"/>
-      <c r="AA15" s="5"/>
-    </row>
-    <row r="16" spans="1:27" ht="15">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
-      <c r="Z16" s="5"/>
-      <c r="AA16" s="5"/>
-    </row>
-    <row r="17" spans="1:27" ht="15">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
-      <c r="Z17" s="5"/>
-      <c r="AA17" s="5"/>
-    </row>
-    <row r="18" spans="1:27" ht="15">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5"/>
-      <c r="Z18" s="5"/>
-      <c r="AA18" s="5"/>
-    </row>
-    <row r="19" spans="1:27" ht="15">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5"/>
-      <c r="Z19" s="5"/>
-      <c r="AA19" s="5"/>
-    </row>
-    <row r="20" spans="1:27" s="5" customFormat="1" ht="15"/>
-    <row r="21" spans="1:27" ht="15">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5"/>
-      <c r="AA21" s="5"/>
-    </row>
-    <row r="22" spans="1:27" ht="15">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
-    </row>
-    <row r="23" spans="1:27" ht="15">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5"/>
-      <c r="AA23" s="5"/>
-    </row>
-    <row r="24" spans="1:27" ht="15">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="5"/>
-      <c r="AA24" s="5"/>
-    </row>
-    <row r="25" spans="1:27" ht="15">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="5"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
-      <c r="Z25" s="5"/>
-      <c r="AA25" s="5"/>
-    </row>
-    <row r="26" spans="1:27" ht="15">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
-      <c r="X26" s="5"/>
-      <c r="Y26" s="5"/>
-      <c r="Z26" s="5"/>
-      <c r="AA26" s="5"/>
-    </row>
-    <row r="27" spans="1:27" ht="15">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="5"/>
-      <c r="X27" s="5"/>
-      <c r="Y27" s="5"/>
-      <c r="Z27" s="5"/>
-      <c r="AA27" s="5"/>
-    </row>
-    <row r="28" spans="1:27" ht="15">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="5"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="5"/>
-      <c r="X28" s="5"/>
-      <c r="Y28" s="5"/>
-      <c r="Z28" s="5"/>
-      <c r="AA28" s="5"/>
-    </row>
-    <row r="29" spans="1:27" ht="15">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="5"/>
-      <c r="V29" s="5"/>
-      <c r="W29" s="5"/>
-      <c r="X29" s="5"/>
-      <c r="Y29" s="5"/>
-      <c r="Z29" s="5"/>
-      <c r="AA29" s="5"/>
-    </row>
-    <row r="30" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
-      <c r="M30"/>
-      <c r="N30"/>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-      <c r="R30"/>
-      <c r="S30"/>
-      <c r="T30"/>
-      <c r="U30"/>
-      <c r="V30"/>
-      <c r="W30"/>
-      <c r="X30"/>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30"/>
-    </row>
+    <row r="11" spans="1:27" ht="15"/>
+    <row r="12" spans="1:27" ht="15"/>
+    <row r="13" spans="1:27" ht="15"/>
+    <row r="14" spans="1:27" ht="15"/>
+    <row r="15" spans="1:27" ht="15"/>
+    <row r="16" spans="1:27" ht="15"/>
+    <row r="17" spans="1:27" ht="15"/>
+    <row r="18" spans="1:27" ht="15"/>
+    <row r="19" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19"/>
+      <c r="AA19"/>
+    </row>
+    <row r="20" spans="1:27" ht="15"/>
+    <row r="21" spans="1:27" ht="15"/>
+    <row r="22" spans="1:27" ht="15"/>
+    <row r="23" spans="1:27" ht="15"/>
+    <row r="24" spans="1:27" ht="15"/>
+    <row r="25" spans="1:27" ht="15"/>
+    <row r="26" spans="1:27" ht="15"/>
+    <row r="27" spans="1:27" ht="15"/>
+    <row r="28" spans="1:27" ht="15"/>
+    <row r="29" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+      <c r="S29"/>
+      <c r="T29"/>
+      <c r="U29"/>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+      <c r="Y29"/>
+      <c r="Z29"/>
+      <c r="AA29"/>
+    </row>
+    <row r="30" spans="1:27" ht="15"/>
     <row r="31" spans="1:27" ht="15"/>
     <row r="32" spans="1:27" ht="15"/>
     <row r="33" spans="1:27" ht="15"/>
@@ -7262,36 +5754,36 @@
     <row r="38" spans="1:27" ht="15"/>
     <row r="39" spans="1:27" ht="15"/>
     <row r="40" spans="1:27" ht="15"/>
-    <row r="41" spans="1:27" ht="15"/>
-    <row r="42" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A42"/>
-      <c r="B42"/>
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="L42"/>
-      <c r="M42"/>
-      <c r="N42"/>
-      <c r="O42"/>
-      <c r="P42"/>
-      <c r="Q42"/>
-      <c r="R42"/>
-      <c r="S42"/>
-      <c r="T42"/>
-      <c r="U42"/>
-      <c r="V42"/>
-      <c r="W42"/>
-      <c r="X42"/>
-      <c r="Y42"/>
-      <c r="Z42"/>
-      <c r="AA42"/>
-    </row>
+    <row r="41" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+      <c r="S41"/>
+      <c r="T41"/>
+      <c r="U41"/>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+      <c r="Y41"/>
+      <c r="Z41"/>
+      <c r="AA41"/>
+    </row>
+    <row r="42" spans="1:27" ht="15"/>
     <row r="43" spans="1:27" ht="15"/>
     <row r="44" spans="1:27" ht="15"/>
     <row r="45" spans="1:27" ht="15"/>
@@ -7302,36 +5794,36 @@
     <row r="50" spans="1:27" ht="15"/>
     <row r="51" spans="1:27" ht="15"/>
     <row r="52" spans="1:27" ht="15"/>
-    <row r="53" spans="1:27" ht="15"/>
-    <row r="54" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A54"/>
-      <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-      <c r="K54"/>
-      <c r="L54"/>
-      <c r="M54"/>
-      <c r="N54"/>
-      <c r="O54"/>
-      <c r="P54"/>
-      <c r="Q54"/>
-      <c r="R54"/>
-      <c r="S54"/>
-      <c r="T54"/>
-      <c r="U54"/>
-      <c r="V54"/>
-      <c r="W54"/>
-      <c r="X54"/>
-      <c r="Y54"/>
-      <c r="Z54"/>
-      <c r="AA54"/>
-    </row>
+    <row r="53" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53"/>
+      <c r="O53"/>
+      <c r="P53"/>
+      <c r="Q53"/>
+      <c r="R53"/>
+      <c r="S53"/>
+      <c r="T53"/>
+      <c r="U53"/>
+      <c r="V53"/>
+      <c r="W53"/>
+      <c r="X53"/>
+      <c r="Y53"/>
+      <c r="Z53"/>
+      <c r="AA53"/>
+    </row>
+    <row r="54" spans="1:27" ht="15"/>
     <row r="55" spans="1:27" ht="15"/>
     <row r="56" spans="1:27" ht="15"/>
     <row r="57" spans="1:27" ht="15"/>
@@ -7342,36 +5834,36 @@
     <row r="62" spans="1:27" ht="15"/>
     <row r="63" spans="1:27" ht="15"/>
     <row r="64" spans="1:27" ht="15"/>
-    <row r="65" spans="1:27" ht="15"/>
-    <row r="66" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A66"/>
-      <c r="B66"/>
-      <c r="C66"/>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-      <c r="K66"/>
-      <c r="L66"/>
-      <c r="M66"/>
-      <c r="N66"/>
-      <c r="O66"/>
-      <c r="P66"/>
-      <c r="Q66"/>
-      <c r="R66"/>
-      <c r="S66"/>
-      <c r="T66"/>
-      <c r="U66"/>
-      <c r="V66"/>
-      <c r="W66"/>
-      <c r="X66"/>
-      <c r="Y66"/>
-      <c r="Z66"/>
-      <c r="AA66"/>
-    </row>
+    <row r="65" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A65"/>
+      <c r="B65"/>
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="M65"/>
+      <c r="N65"/>
+      <c r="O65"/>
+      <c r="P65"/>
+      <c r="Q65"/>
+      <c r="R65"/>
+      <c r="S65"/>
+      <c r="T65"/>
+      <c r="U65"/>
+      <c r="V65"/>
+      <c r="W65"/>
+      <c r="X65"/>
+      <c r="Y65"/>
+      <c r="Z65"/>
+      <c r="AA65"/>
+    </row>
+    <row r="66" spans="1:27" ht="15"/>
     <row r="67" spans="1:27" ht="15"/>
     <row r="68" spans="1:27" ht="15"/>
     <row r="69" spans="1:27" ht="15"/>
@@ -7382,36 +5874,36 @@
     <row r="74" spans="1:27" ht="15"/>
     <row r="75" spans="1:27" ht="15"/>
     <row r="76" spans="1:27" ht="15"/>
-    <row r="77" spans="1:27" ht="15"/>
-    <row r="78" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A78"/>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
-      <c r="I78"/>
-      <c r="J78"/>
-      <c r="K78"/>
-      <c r="L78"/>
-      <c r="M78"/>
-      <c r="N78"/>
-      <c r="O78"/>
-      <c r="P78"/>
-      <c r="Q78"/>
-      <c r="R78"/>
-      <c r="S78"/>
-      <c r="T78"/>
-      <c r="U78"/>
-      <c r="V78"/>
-      <c r="W78"/>
-      <c r="X78"/>
-      <c r="Y78"/>
-      <c r="Z78"/>
-      <c r="AA78"/>
-    </row>
+    <row r="77" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77"/>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77"/>
+      <c r="I77"/>
+      <c r="J77"/>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="M77"/>
+      <c r="N77"/>
+      <c r="O77"/>
+      <c r="P77"/>
+      <c r="Q77"/>
+      <c r="R77"/>
+      <c r="S77"/>
+      <c r="T77"/>
+      <c r="U77"/>
+      <c r="V77"/>
+      <c r="W77"/>
+      <c r="X77"/>
+      <c r="Y77"/>
+      <c r="Z77"/>
+      <c r="AA77"/>
+    </row>
+    <row r="78" spans="1:27" ht="15"/>
     <row r="79" spans="1:27" ht="15"/>
     <row r="80" spans="1:27" ht="15"/>
     <row r="81" spans="1:27" ht="15"/>
@@ -7422,36 +5914,36 @@
     <row r="86" spans="1:27" ht="15"/>
     <row r="87" spans="1:27" ht="15"/>
     <row r="88" spans="1:27" ht="15"/>
-    <row r="89" spans="1:27" ht="15"/>
-    <row r="90" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A90"/>
-      <c r="B90"/>
-      <c r="C90"/>
-      <c r="D90"/>
-      <c r="E90"/>
-      <c r="F90"/>
-      <c r="G90"/>
-      <c r="H90"/>
-      <c r="I90"/>
-      <c r="J90"/>
-      <c r="K90"/>
-      <c r="L90"/>
-      <c r="M90"/>
-      <c r="N90"/>
-      <c r="O90"/>
-      <c r="P90"/>
-      <c r="Q90"/>
-      <c r="R90"/>
-      <c r="S90"/>
-      <c r="T90"/>
-      <c r="U90"/>
-      <c r="V90"/>
-      <c r="W90"/>
-      <c r="X90"/>
-      <c r="Y90"/>
-      <c r="Z90"/>
-      <c r="AA90"/>
-    </row>
+    <row r="89" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89"/>
+      <c r="G89"/>
+      <c r="H89"/>
+      <c r="I89"/>
+      <c r="J89"/>
+      <c r="K89"/>
+      <c r="L89"/>
+      <c r="M89"/>
+      <c r="N89"/>
+      <c r="O89"/>
+      <c r="P89"/>
+      <c r="Q89"/>
+      <c r="R89"/>
+      <c r="S89"/>
+      <c r="T89"/>
+      <c r="U89"/>
+      <c r="V89"/>
+      <c r="W89"/>
+      <c r="X89"/>
+      <c r="Y89"/>
+      <c r="Z89"/>
+      <c r="AA89"/>
+    </row>
+    <row r="90" spans="1:27" ht="15"/>
     <row r="91" spans="1:27" ht="15"/>
     <row r="92" spans="1:27" ht="15"/>
     <row r="93" spans="1:27" ht="15"/>
@@ -7462,36 +5954,36 @@
     <row r="98" spans="1:27" ht="15"/>
     <row r="99" spans="1:27" ht="15"/>
     <row r="100" spans="1:27" ht="15"/>
-    <row r="101" spans="1:27" ht="15"/>
-    <row r="102" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A102"/>
-      <c r="B102"/>
-      <c r="C102"/>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
-      <c r="I102"/>
-      <c r="J102"/>
-      <c r="K102"/>
-      <c r="L102"/>
-      <c r="M102"/>
-      <c r="N102"/>
-      <c r="O102"/>
-      <c r="P102"/>
-      <c r="Q102"/>
-      <c r="R102"/>
-      <c r="S102"/>
-      <c r="T102"/>
-      <c r="U102"/>
-      <c r="V102"/>
-      <c r="W102"/>
-      <c r="X102"/>
-      <c r="Y102"/>
-      <c r="Z102"/>
-      <c r="AA102"/>
-    </row>
+    <row r="101" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
+      <c r="L101"/>
+      <c r="M101"/>
+      <c r="N101"/>
+      <c r="O101"/>
+      <c r="P101"/>
+      <c r="Q101"/>
+      <c r="R101"/>
+      <c r="S101"/>
+      <c r="T101"/>
+      <c r="U101"/>
+      <c r="V101"/>
+      <c r="W101"/>
+      <c r="X101"/>
+      <c r="Y101"/>
+      <c r="Z101"/>
+      <c r="AA101"/>
+    </row>
+    <row r="102" spans="1:27" ht="15"/>
     <row r="103" spans="1:27" ht="15"/>
     <row r="104" spans="1:27" ht="15"/>
     <row r="105" spans="1:27" ht="15"/>
@@ -7502,36 +5994,36 @@
     <row r="110" spans="1:27" ht="15"/>
     <row r="111" spans="1:27" ht="15"/>
     <row r="112" spans="1:27" ht="15"/>
-    <row r="113" spans="1:28" ht="15"/>
-    <row r="114" spans="1:28" s="5" customFormat="1" ht="15">
-      <c r="A114"/>
-      <c r="B114"/>
-      <c r="C114"/>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
-      <c r="G114"/>
-      <c r="H114"/>
-      <c r="I114"/>
-      <c r="J114"/>
-      <c r="K114"/>
-      <c r="L114"/>
-      <c r="M114"/>
-      <c r="N114"/>
-      <c r="O114"/>
-      <c r="P114"/>
-      <c r="Q114"/>
-      <c r="R114"/>
-      <c r="S114"/>
-      <c r="T114"/>
-      <c r="U114"/>
-      <c r="V114"/>
-      <c r="W114"/>
-      <c r="X114"/>
-      <c r="Y114"/>
-      <c r="Z114"/>
-      <c r="AA114"/>
-    </row>
+    <row r="113" spans="1:28" s="5" customFormat="1" ht="15">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="I113"/>
+      <c r="J113"/>
+      <c r="K113"/>
+      <c r="L113"/>
+      <c r="M113"/>
+      <c r="N113"/>
+      <c r="O113"/>
+      <c r="P113"/>
+      <c r="Q113"/>
+      <c r="R113"/>
+      <c r="S113"/>
+      <c r="T113"/>
+      <c r="U113"/>
+      <c r="V113"/>
+      <c r="W113"/>
+      <c r="X113"/>
+      <c r="Y113"/>
+      <c r="Z113"/>
+      <c r="AA113"/>
+    </row>
+    <row r="114" spans="1:28" ht="15"/>
     <row r="115" spans="1:28" ht="15"/>
     <row r="116" spans="1:28" ht="15"/>
     <row r="117" spans="1:28" ht="15"/>
@@ -7539,35 +6031,37 @@
     <row r="119" spans="1:28" ht="15"/>
     <row r="120" spans="1:28" ht="15"/>
     <row r="121" spans="1:28" ht="15"/>
-    <row r="122" spans="1:28" ht="15"/>
-    <row r="123" spans="1:28" s="5" customFormat="1" ht="15">
-      <c r="A123"/>
-      <c r="B123"/>
-      <c r="C123"/>
-      <c r="D123"/>
-      <c r="E123"/>
-      <c r="F123"/>
-      <c r="G123"/>
-      <c r="H123"/>
-      <c r="I123"/>
-      <c r="J123"/>
-      <c r="K123"/>
-      <c r="L123"/>
-      <c r="M123"/>
-      <c r="N123"/>
-      <c r="O123"/>
-      <c r="P123"/>
-      <c r="Q123"/>
-      <c r="R123"/>
-      <c r="S123"/>
-      <c r="T123"/>
-      <c r="U123"/>
-      <c r="V123"/>
-      <c r="W123"/>
-      <c r="X123"/>
-      <c r="Y123"/>
-      <c r="Z123"/>
-      <c r="AA123"/>
+    <row r="122" spans="1:28" s="5" customFormat="1" ht="15">
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="H122"/>
+      <c r="I122"/>
+      <c r="J122"/>
+      <c r="K122"/>
+      <c r="L122"/>
+      <c r="M122"/>
+      <c r="N122"/>
+      <c r="O122"/>
+      <c r="P122"/>
+      <c r="Q122"/>
+      <c r="R122"/>
+      <c r="S122"/>
+      <c r="T122"/>
+      <c r="U122"/>
+      <c r="V122"/>
+      <c r="W122"/>
+      <c r="X122"/>
+      <c r="Y122"/>
+      <c r="Z122"/>
+      <c r="AA122"/>
+    </row>
+    <row r="123" spans="1:28" ht="15">
+      <c r="AB123" s="5"/>
     </row>
     <row r="124" spans="1:28" ht="15">
       <c r="AB124" s="5"/>
@@ -7617,9 +6111,7 @@
     <row r="139" spans="28:28" ht="15">
       <c r="AB139" s="5"/>
     </row>
-    <row r="140" spans="28:28" ht="15">
-      <c r="AB140" s="5"/>
-    </row>
+    <row r="140" spans="28:28" ht="15"/>
     <row r="141" spans="28:28" ht="15"/>
     <row r="142" spans="28:28" ht="15"/>
     <row r="143" spans="28:28" ht="15"/>
@@ -7649,13 +6141,12 @@
     <row r="167" ht="15"/>
     <row r="168" ht="15"/>
     <row r="169" ht="15"/>
-    <row r="170" ht="15"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 P2:R2 Z4:AA11 V2:X2 H4:L11 D2:F2 D4:F11 N4:R11 T4:X11" name="LAS"/>
-    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 Y4:Y11 G4:G11 M4:M11 S4:S11" name="SOURCE"/>
-    <protectedRange sqref="C4:C11" name="Textbooks_1"/>
+    <protectedRange sqref="J2:L2 P2:R2 Z3:AA10 V2:X2 H3:L10 D2:F2 D3:F10 N3:R10 T3:X10" name="LAS"/>
+    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 Y3:Y10 G3:G10 M3:M10 S3:S10" name="SOURCE"/>
+    <protectedRange sqref="C3:C10" name="Textbooks_1"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -7665,10 +6156,10 @@
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S4:S11 Y4:Y11 G4:G11 M4:M11" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S10 Y3:Y10 G3:G10 M3:M10" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X4:X11 F4:F11 L4:L11 R4:R11" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X10 F3:F10 L3:L10 R3:R10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
   </dataValidations>
